--- a/05_Testovanie/zistene-chyby.xlsx
+++ b/05_Testovanie/zistene-chyby.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Papo\source\repos\Rocnikovy_stick_fight\dokumentacia\Stickops\05_Testovanie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CF38629-BEBF-471C-B847-8494859E8A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{388D731E-9BF0-41FF-8547-2DBA1305CDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7F4F19A-ACC2-4012-8280-C78C3F4A5389}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39CF7D06-1778-4F9B-BEE1-4F44CFAE65D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Zistené chyby" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ID</t>
   </si>
@@ -60,123 +60,6 @@
   </si>
   <si>
     <t>Commit</t>
-  </si>
-  <si>
-    <t>BUG-01</t>
-  </si>
-  <si>
-    <t>Pevný blok: na rohu bloku sa nesprávne vyhodnocovala kolízia (postava sa zasekla alebo prepadla).</t>
-  </si>
-  <si>
-    <t>Skočiť šikmo na roh pevného bloku v aréne.</t>
-  </si>
-  <si>
-    <t>Stredná</t>
-  </si>
-  <si>
-    <t>Opravené</t>
-  </si>
-  <si>
-    <t>7b2aa8b</t>
-  </si>
-  <si>
-    <t>BUG-02</t>
-  </si>
-  <si>
-    <t>AI bossovia nevedeli vyliezť za hráčom na vyššie plošinky – hráč sa mohol schovať.</t>
-  </si>
-  <si>
-    <t>Vyskočiť na najvyššiu plošinku a čakať.</t>
-  </si>
-  <si>
-    <t>Vysoká</t>
-  </si>
-  <si>
-    <t>Opravené – navigácia AI, test test_ai_navigation.cpp</t>
-  </si>
-  <si>
-    <t>BUG-03</t>
-  </si>
-  <si>
-    <t>Rozmazané písmo v logu, nadpisoch aj malom texte.</t>
-  </si>
-  <si>
-    <t>Spustiť hru na celú obrazovku.</t>
-  </si>
-  <si>
-    <t>Nízka</t>
-  </si>
-  <si>
-    <t>Opravené – písmo vo vysokom rozlíšení s mipmapami</t>
-  </si>
-  <si>
-    <t>7bd4fe0</t>
-  </si>
-  <si>
-    <t>BUG-04</t>
-  </si>
-  <si>
-    <t>F11 (celá obrazovka) nefungovalo na všetkých obrazovkách.</t>
-  </si>
-  <si>
-    <t>V rôznych menu stlačiť F11.</t>
-  </si>
-  <si>
-    <t>967c55d</t>
-  </si>
-  <si>
-    <t>BUG-05</t>
-  </si>
-  <si>
-    <t>W + útok spúšťal skok namiesto útoku hore (uppercut).</t>
-  </si>
-  <si>
-    <t>Stlačiť naraz W a K.</t>
-  </si>
-  <si>
-    <t>Opravené – skok presunutý na Space, test „Hore + útok naraz = uppercut“</t>
-  </si>
-  <si>
-    <t>3b68630</t>
-  </si>
-  <si>
-    <t>BUG-06</t>
-  </si>
-  <si>
-    <t>Tréner zobrazoval zlý názov akcie pre smer hore.</t>
-  </si>
-  <si>
-    <t>Otvoriť stick_trainer, sledovať akcie AI.</t>
-  </si>
-  <si>
-    <t>bee5208</t>
-  </si>
-  <si>
-    <t>BUG-07</t>
-  </si>
-  <si>
-    <t>Staré testovacie programy v build\windows-vs\bin\Release (z 8. 10.) hlásili 9 zlyhaných testov – nezodpovedali aktuálnemu obsahu.</t>
-  </si>
-  <si>
-    <t>Spustiť build\windows-vs\bin\Release\stick_tests.exe bez nového zostavenia.</t>
-  </si>
-  <si>
-    <t>Vyriešené – po zostavení prechádzajú všetky testy (build\windows-vs\tests)</t>
-  </si>
-  <si>
-    <t>–</t>
-  </si>
-  <si>
-    <t>BUG-08</t>
-  </si>
-  <si>
-    <t>Zmena kláves sa nedá urobiť v menu, iba úpravou content/settings/input.json.</t>
-  </si>
-  <si>
-    <t>NASTAVENIA › Ovládanie.</t>
-  </si>
-  <si>
-    <t>Otvorené (požiadavka FR-006, priorita C)</t>
   </si>
 </sst>
 </file>
@@ -242,15 +125,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -586,8 +463,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6139A486-7D11-4621-9A65-11581B41428D}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0258DC-7973-4FA1-BAF5-6FF6FD86D763}">
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -622,190 +499,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3">
-        <v>46302</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46302</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46302</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3">
-        <v>46301</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46301</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46301</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46311</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46311</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
